--- a/example_project/Analysis/MG_motility/average_motility.xlsx
+++ b/example_project/Analysis/MG_motility/average_motility.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,170 +413,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>project tag</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>tag folders</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>projection center</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source image</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
         <is>
           <t>avrg Stable</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Stable std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>avrg Gain</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Gain std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
         <is>
           <t>avrg Loss</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Loss std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>avrg rel Stable</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>rel Stable std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>avrg rel Gain</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>rel Gain std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>avrg rel Loss</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>rel Loss std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
         <is>
           <t>avrg tor</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Stable std</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Gain std</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Loss std</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>rel Stable std</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>rel Gain std</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>rel Loss std</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>tor std</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1</t>
+        </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>TP000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TP000</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>projection_center_23</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>408853.4285714286</v>
+          <t>projection_center_28</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ID240103_P17_1/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>212977.7142857143</v>
+        <v>582181.8571428572</v>
       </c>
       <c r="G2" t="n">
-        <v>216374.2857142857</v>
+        <v>13846.77516522134</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4876912320318161</v>
+        <v>217152.2857142857</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2540857694915845</v>
+        <v>10046.4746837599</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2582229984765993</v>
+        <v>218908</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5123087679681838</v>
+        <v>7473.681399863568</v>
       </c>
       <c r="L2" t="n">
-        <v>22924.65691387872</v>
+        <v>0.5717789759031897</v>
       </c>
       <c r="M2" t="n">
-        <v>19905.74116274235</v>
+        <v>0.0142820818389344</v>
       </c>
       <c r="N2" t="n">
-        <v>10584.34603103857</v>
+        <v>0.2132424436939507</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02233880879013702</v>
+        <v>0.009168107943983865</v>
       </c>
       <c r="P2" t="n">
-        <v>0.02267417200199065</v>
+        <v>0.2149785804028595</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0130136532055444</v>
+        <v>0.006895746288671</v>
       </c>
       <c r="R2" t="n">
-        <v>0.022338808790137</v>
+        <v>0.4282210240968102</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01428208183893442</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3</t>
+        </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ID240103_P17_1</t>
+          <t>TP000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TP000</t>
+          <t>TP000/registered</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -596,108 +603,51 @@
           <t>projection_center_28</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>582181.8571428572</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ID240321_P17_3/TP000/registered/all stacks 4D reg.tif</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>217152.2857142857</v>
+        <v>580679.2857142857</v>
       </c>
       <c r="G3" t="n">
-        <v>218908</v>
+        <v>13061.44687894219</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5717789759031897</v>
+        <v>206281.1428571429</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2132424436939507</v>
+        <v>6272.93398733988</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2149785804028595</v>
+        <v>208065.2857142857</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4282210240968102</v>
+        <v>8323.599055582581</v>
       </c>
       <c r="L3" t="n">
-        <v>13846.77516522134</v>
+        <v>0.5835891054611285</v>
       </c>
       <c r="M3" t="n">
-        <v>10046.4746837599</v>
+        <v>0.013366461555454</v>
       </c>
       <c r="N3" t="n">
-        <v>7473.681399863568</v>
+        <v>0.2073160053032103</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0142820818389344</v>
+        <v>0.006413516356885376</v>
       </c>
       <c r="P3" t="n">
-        <v>0.009168107943983865</v>
+        <v>0.2090948892356612</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.006895746288671</v>
+        <v>0.008040406915448274</v>
       </c>
       <c r="R3" t="n">
-        <v>0.01428208183893442</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ID240321_P17_3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TP000</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>projection_center_28</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>580679.2857142857</v>
-      </c>
-      <c r="F4" t="n">
-        <v>206281.1428571429</v>
-      </c>
-      <c r="G4" t="n">
-        <v>208065.2857142857</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.5835891054611285</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.2073160053032103</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.2090948892356612</v>
-      </c>
-      <c r="K4" t="n">
         <v>0.4164108945388715</v>
       </c>
-      <c r="L4" t="n">
-        <v>13061.44687894219</v>
-      </c>
-      <c r="M4" t="n">
-        <v>6272.93398733988</v>
-      </c>
-      <c r="N4" t="n">
-        <v>8323.599055582581</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.013366461555454</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.006413516356885376</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.008040406915448274</v>
-      </c>
-      <c r="R4" t="n">
+      <c r="S3" t="n">
         <v>0.01336646155545401</v>
       </c>
     </row>
